--- a/Agustus-2026.xlsx
+++ b/Agustus-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E22AA78-A4FA-4532-8120-07289FB08FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{269E6FB9-E4F7-4920-9381-60E53D88FCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -572,16 +572,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="4">
-        <v>206</v>
+        <v>888</v>
       </c>
       <c r="C2" s="4">
-        <v>513</v>
+        <v>1357</v>
       </c>
       <c r="D2" s="9">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="E2" s="13">
-        <v>2.75</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -591,16 +591,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>174</v>
+        <v>585</v>
       </c>
       <c r="C3" s="4">
-        <v>591</v>
+        <v>1418</v>
       </c>
       <c r="D3" s="9">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="E3" s="13">
-        <v>3</v>
+        <v>2.5714285714285716</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -610,16 +610,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="4">
-        <v>204</v>
+        <v>696</v>
       </c>
       <c r="C4" s="4">
-        <v>680</v>
+        <v>1626</v>
       </c>
       <c r="D4" s="9">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="E4" s="13">
-        <v>3.125</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -629,16 +629,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>176</v>
+        <v>647</v>
       </c>
       <c r="C5" s="4">
-        <v>599</v>
+        <v>1414</v>
       </c>
       <c r="D5" s="9">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="E5" s="13">
-        <v>2.625</v>
+        <v>3.5238095238095237</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -648,16 +648,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="4">
-        <v>180</v>
+        <v>686</v>
       </c>
       <c r="C6" s="4">
-        <v>470</v>
+        <v>1262</v>
       </c>
       <c r="D6" s="9">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="E6" s="13">
-        <v>3.375</v>
+        <v>4.0952380952380949</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -667,16 +667,16 @@
         <v>23</v>
       </c>
       <c r="B7" s="4">
-        <v>144</v>
+        <v>331</v>
       </c>
       <c r="C7" s="4">
-        <v>238</v>
+        <v>412</v>
       </c>
       <c r="D7" s="9">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E7" s="13">
-        <v>1.25</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -686,16 +686,16 @@
         <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>155</v>
+        <v>612</v>
       </c>
       <c r="C8" s="4">
-        <v>556</v>
+        <v>1606</v>
       </c>
       <c r="D8" s="9">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="E8" s="13">
-        <v>1.625</v>
+        <v>3.0952380952380953</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -705,16 +705,16 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>172</v>
+        <v>679</v>
       </c>
       <c r="C9" s="4">
-        <v>614</v>
+        <v>1659</v>
       </c>
       <c r="D9" s="9">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="E9" s="13">
-        <v>2.25</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -724,16 +724,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>183</v>
+        <v>649</v>
       </c>
       <c r="C10" s="4">
-        <v>529</v>
+        <v>1412</v>
       </c>
       <c r="D10" s="9">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="E10" s="13">
-        <v>2.625</v>
+        <v>3.4285714285714284</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -743,16 +743,16 @@
         <v>12</v>
       </c>
       <c r="B11" s="4">
-        <v>155</v>
+        <v>471</v>
       </c>
       <c r="C11" s="4">
-        <v>582</v>
+        <v>1636</v>
       </c>
       <c r="D11" s="9">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="E11" s="13">
-        <v>3.875</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -762,16 +762,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="4">
-        <v>252</v>
+        <v>745</v>
       </c>
       <c r="C12" s="4">
-        <v>571</v>
+        <v>1425</v>
       </c>
       <c r="D12" s="9">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="E12" s="13">
-        <v>3.5</v>
+        <v>3.8095238095238093</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -781,16 +781,16 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>131</v>
+        <v>391</v>
       </c>
       <c r="C13" s="4">
-        <v>358</v>
+        <v>1117</v>
       </c>
       <c r="D13" s="9">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="E13" s="13">
-        <v>1.125</v>
+        <v>3.1428571428571428</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -800,16 +800,16 @@
         <v>15</v>
       </c>
       <c r="B14" s="4">
-        <v>247</v>
+        <v>694</v>
       </c>
       <c r="C14" s="4">
-        <v>570</v>
+        <v>1352</v>
       </c>
       <c r="D14" s="9">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E14" s="13">
-        <v>2.125</v>
+        <v>2.1904761904761907</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -819,16 +819,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>138</v>
+        <v>462</v>
       </c>
       <c r="C15" s="4">
-        <v>599</v>
+        <v>1559</v>
       </c>
       <c r="D15" s="9">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E15" s="13">
-        <v>1.75</v>
+        <v>2.1904761904761907</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -838,16 +838,16 @@
         <v>24</v>
       </c>
       <c r="B16" s="4">
-        <v>173</v>
+        <v>687</v>
       </c>
       <c r="C16" s="4">
-        <v>492</v>
+        <v>1453</v>
       </c>
       <c r="D16" s="9">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="E16" s="13">
-        <v>3.75</v>
+        <v>3.1904761904761907</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -857,16 +857,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>159</v>
+        <v>557</v>
       </c>
       <c r="C17" s="4">
-        <v>616</v>
+        <v>1648</v>
       </c>
       <c r="D17" s="9">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="E17" s="13">
-        <v>1.75</v>
+        <v>2.9047619047619047</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -876,16 +876,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="4">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="C18" s="4">
-        <v>579</v>
+        <v>1268</v>
       </c>
       <c r="D18" s="9">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E18" s="13">
-        <v>1.5</v>
+        <v>1.1904761904761905</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -895,16 +895,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="4">
-        <v>134</v>
+        <v>503</v>
       </c>
       <c r="C19" s="4">
-        <v>562</v>
+        <v>1650</v>
       </c>
       <c r="D19" s="9">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="E19" s="13">
-        <v>2.125</v>
+        <v>3.1428571428571428</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -912,16 +912,16 @@
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>3077</v>
+        <v>10539</v>
       </c>
       <c r="C20" s="6">
-        <v>9719</v>
+        <v>25274</v>
       </c>
       <c r="D20" s="10">
-        <v>353</v>
+        <v>1137</v>
       </c>
       <c r="E20" s="14">
-        <v>2.4513888888888888</v>
+        <v>3.0079365079365079</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1113,63 +1113,81 @@
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4">
-        <v>0</v>
-      </c>
+      <c r="B2" s="4"/>
       <c r="C2" s="4">
         <v>0</v>
       </c>
       <c r="D2" s="4">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="E2" s="4">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="F2" s="4">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="G2" s="4">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="H2" s="4">
-        <v>93</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="I2" s="4"/>
       <c r="J2" s="4">
         <v>0</v>
       </c>
       <c r="K2" s="4">
-        <v>92</v>
-      </c>
-      <c r="L2" s="4">
-        <v>0</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="L2" s="4"/>
       <c r="M2" s="4">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
+      <c r="O2" s="4">
+        <v>108</v>
+      </c>
+      <c r="P2" s="4">
+        <v>123</v>
+      </c>
       <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
+      <c r="R2" s="4">
+        <v>132</v>
+      </c>
+      <c r="S2" s="4">
+        <v>131</v>
+      </c>
+      <c r="T2" s="4">
+        <v>119</v>
+      </c>
       <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
+      <c r="V2" s="4">
+        <v>105</v>
+      </c>
+      <c r="W2" s="4">
+        <v>112</v>
+      </c>
       <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
+      <c r="Y2" s="4">
+        <v>117</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>98</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>115</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>108</v>
+      </c>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
       <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
+      <c r="AF2" s="4">
+        <v>124</v>
+      </c>
       <c r="AG2" s="9">
-        <v>719</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -1177,314 +1195,400 @@
         <v>6</v>
       </c>
       <c r="B3" s="4">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C3" s="4">
         <v>0</v>
       </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
+      <c r="D3" s="4"/>
       <c r="E3" s="4">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="F3" s="4">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="G3" s="4">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="H3" s="4">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="I3" s="4">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="J3" s="4">
         <v>0</v>
       </c>
       <c r="K3" s="4">
-        <v>72</v>
-      </c>
-      <c r="L3" s="4">
-        <v>0</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="L3" s="4"/>
       <c r="M3" s="4">
-        <v>101</v>
-      </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+        <v>120</v>
+      </c>
+      <c r="N3" s="4">
+        <v>100</v>
+      </c>
+      <c r="O3" s="4">
+        <v>109</v>
+      </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
+      <c r="R3" s="4">
+        <v>116</v>
+      </c>
+      <c r="S3" s="4">
+        <v>123</v>
+      </c>
+      <c r="T3" s="4">
+        <v>100</v>
+      </c>
+      <c r="U3" s="4">
+        <v>94</v>
+      </c>
+      <c r="V3" s="4">
+        <v>106</v>
+      </c>
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
+      <c r="AB3" s="4">
+        <v>110</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>118</v>
+      </c>
+      <c r="AD3" s="4">
+        <v>144</v>
+      </c>
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="9">
-        <v>765</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4">
-        <v>0</v>
-      </c>
+      <c r="B4" s="4"/>
       <c r="C4" s="4">
         <v>0</v>
       </c>
       <c r="D4" s="4">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E4" s="4">
-        <v>112</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="F4" s="4"/>
       <c r="G4" s="4">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="H4" s="4">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I4" s="4">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="J4" s="4">
         <v>0</v>
       </c>
       <c r="K4" s="4">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="L4" s="4">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="M4" s="4">
+        <v>114</v>
+      </c>
+      <c r="N4" s="4">
+        <v>106</v>
+      </c>
+      <c r="O4" s="4">
         <v>100</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
+      <c r="S4" s="4">
+        <v>132</v>
+      </c>
+      <c r="T4" s="4">
+        <v>116</v>
+      </c>
       <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
+      <c r="V4" s="4">
+        <v>118</v>
+      </c>
+      <c r="W4" s="4">
+        <v>113</v>
+      </c>
       <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
+      <c r="Y4" s="4">
+        <v>117</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>104</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>121</v>
+      </c>
+      <c r="AB4" s="4">
+        <v>101</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>100</v>
+      </c>
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
-      <c r="AF4" s="4"/>
+      <c r="AF4" s="4">
+        <v>112</v>
+      </c>
       <c r="AG4" s="9">
-        <v>884</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4">
-        <v>0</v>
-      </c>
+      <c r="B5" s="4"/>
       <c r="C5" s="4">
         <v>0</v>
       </c>
       <c r="D5" s="4">
-        <v>99</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="E5" s="4"/>
       <c r="F5" s="4">
+        <v>129</v>
+      </c>
+      <c r="G5" s="4">
+        <v>134</v>
+      </c>
+      <c r="H5" s="4">
+        <v>119</v>
+      </c>
+      <c r="I5" s="4">
+        <v>77</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <v>91</v>
+      </c>
+      <c r="L5" s="4">
         <v>124</v>
       </c>
-      <c r="G5" s="4">
-        <v>117</v>
-      </c>
-      <c r="H5" s="4">
-        <v>100</v>
-      </c>
-      <c r="I5" s="4">
-        <v>63</v>
-      </c>
-      <c r="J5" s="4">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4">
-        <v>78</v>
-      </c>
-      <c r="L5" s="4">
-        <v>105</v>
-      </c>
       <c r="M5" s="4">
-        <v>89</v>
-      </c>
-      <c r="N5" s="4"/>
+        <v>102</v>
+      </c>
+      <c r="N5" s="4">
+        <v>102</v>
+      </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
+      <c r="R5" s="4">
+        <v>101</v>
+      </c>
+      <c r="S5" s="4">
+        <v>115</v>
+      </c>
+      <c r="T5" s="4">
+        <v>105</v>
+      </c>
+      <c r="U5" s="4">
+        <v>109</v>
+      </c>
+      <c r="V5" s="4">
+        <v>99</v>
+      </c>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
+      <c r="Y5" s="4">
+        <v>114</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>106</v>
+      </c>
       <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
+      <c r="AB5" s="4">
+        <v>112</v>
+      </c>
       <c r="AC5" s="4"/>
-      <c r="AD5" s="4"/>
+      <c r="AD5" s="4">
+        <v>112</v>
+      </c>
       <c r="AE5" s="4"/>
-      <c r="AF5" s="4"/>
+      <c r="AF5" s="4">
+        <v>99</v>
+      </c>
       <c r="AG5" s="9">
-        <v>775</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="4">
-        <v>0</v>
-      </c>
+      <c r="B6" s="4"/>
       <c r="C6" s="4">
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E6" s="4">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F6" s="4">
-        <v>88</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="G6" s="4"/>
       <c r="H6" s="4">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="I6" s="4">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J6" s="4">
         <v>0</v>
       </c>
-      <c r="K6" s="4">
-        <v>0</v>
-      </c>
+      <c r="K6" s="4"/>
       <c r="L6" s="4">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M6" s="4">
-        <v>95</v>
-      </c>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="N6" s="4">
+        <v>102</v>
+      </c>
+      <c r="O6" s="4">
+        <v>109</v>
+      </c>
+      <c r="P6" s="4">
+        <v>109</v>
+      </c>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
+      <c r="T6" s="4">
+        <v>60</v>
+      </c>
+      <c r="U6" s="4">
+        <v>73</v>
+      </c>
+      <c r="V6" s="4">
+        <v>77</v>
+      </c>
+      <c r="W6" s="4">
+        <v>82</v>
+      </c>
       <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
+      <c r="Y6" s="4">
+        <v>109</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>102</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>112</v>
+      </c>
       <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
-      <c r="AD6" s="4"/>
+      <c r="AC6" s="4">
+        <v>109</v>
+      </c>
+      <c r="AD6" s="4">
+        <v>140</v>
+      </c>
       <c r="AE6" s="4"/>
-      <c r="AF6" s="4"/>
+      <c r="AF6" s="4">
+        <v>75</v>
+      </c>
       <c r="AG6" s="9">
-        <v>650</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="4">
-        <v>0</v>
-      </c>
+      <c r="B7" s="4"/>
       <c r="C7" s="4">
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E7" s="4">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F7" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="4">
-        <v>67</v>
-      </c>
-      <c r="I7" s="4">
-        <v>0</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I7" s="4"/>
       <c r="J7" s="4">
         <v>0</v>
       </c>
       <c r="K7" s="4">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="L7" s="4">
-        <v>65</v>
-      </c>
-      <c r="M7" s="4">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4">
+        <v>2</v>
+      </c>
+      <c r="O7" s="4">
+        <v>8</v>
+      </c>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
+      <c r="R7" s="4">
+        <v>17</v>
+      </c>
+      <c r="S7" s="4">
+        <v>20</v>
+      </c>
+      <c r="T7" s="4">
+        <v>52</v>
+      </c>
+      <c r="U7" s="4">
+        <v>37</v>
+      </c>
+      <c r="V7" s="4">
+        <v>62</v>
+      </c>
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4"/>
       <c r="AB7" s="4"/>
-      <c r="AC7" s="4"/>
+      <c r="AC7" s="4">
+        <v>59</v>
+      </c>
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
-      <c r="AF7" s="4"/>
+      <c r="AF7" s="4">
+        <v>60</v>
+      </c>
       <c r="AG7" s="9">
-        <v>382</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -1492,62 +1596,80 @@
         <v>9</v>
       </c>
       <c r="B8" s="4">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C8" s="4">
         <v>0</v>
       </c>
       <c r="D8" s="4">
-        <v>102</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="E8" s="4"/>
       <c r="F8" s="4">
-        <v>120</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
-        <v>0</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
       <c r="I8" s="4">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="J8" s="4">
         <v>0</v>
       </c>
       <c r="K8" s="4">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="L8" s="4">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="M8" s="4">
-        <v>102</v>
-      </c>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
+        <v>115</v>
+      </c>
+      <c r="N8" s="4">
+        <v>122</v>
+      </c>
+      <c r="O8" s="4">
+        <v>123</v>
+      </c>
+      <c r="P8" s="4">
+        <v>111</v>
+      </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
+      <c r="S8" s="4">
+        <v>126</v>
+      </c>
+      <c r="T8" s="4">
+        <v>100</v>
+      </c>
+      <c r="U8" s="4">
+        <v>125</v>
+      </c>
+      <c r="V8" s="4">
+        <v>102</v>
+      </c>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
+      <c r="Y8" s="4">
+        <v>117</v>
+      </c>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
-      <c r="AD8" s="4"/>
+      <c r="AB8" s="4">
+        <v>120</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>120</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>152</v>
+      </c>
       <c r="AE8" s="4"/>
-      <c r="AF8" s="4"/>
+      <c r="AF8" s="4">
+        <v>111</v>
+      </c>
       <c r="AG8" s="9">
-        <v>711</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -1555,62 +1677,86 @@
         <v>10</v>
       </c>
       <c r="B9" s="4">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C9" s="4">
         <v>0</v>
       </c>
       <c r="D9" s="4">
-        <v>103</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="E9" s="4"/>
       <c r="F9" s="4">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G9" s="4">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H9" s="4">
-        <v>127</v>
-      </c>
-      <c r="I9" s="4">
-        <v>0</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="I9" s="4"/>
       <c r="J9" s="4">
         <v>0</v>
       </c>
       <c r="K9" s="4">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L9" s="4">
         <v>1</v>
       </c>
       <c r="M9" s="4">
+        <v>129</v>
+      </c>
+      <c r="N9" s="4">
+        <v>106</v>
+      </c>
+      <c r="O9" s="4">
         <v>116</v>
       </c>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
+      <c r="P9" s="4">
+        <v>108</v>
+      </c>
       <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
+      <c r="R9" s="4">
+        <v>111</v>
+      </c>
+      <c r="S9" s="4">
+        <v>124</v>
+      </c>
+      <c r="T9" s="4">
+        <v>83</v>
+      </c>
+      <c r="U9" s="4">
+        <v>99</v>
+      </c>
+      <c r="V9" s="4">
+        <v>89</v>
+      </c>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
-      <c r="AB9" s="4"/>
-      <c r="AC9" s="4"/>
+      <c r="Y9" s="4">
+        <v>105</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>113</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>106</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>120</v>
+      </c>
+      <c r="AC9" s="4">
+        <v>109</v>
+      </c>
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
-      <c r="AF9" s="4"/>
+      <c r="AF9" s="4">
+        <v>105</v>
+      </c>
       <c r="AG9" s="9">
-        <v>786</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1618,188 +1764,244 @@
         <v>11</v>
       </c>
       <c r="B10" s="4">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C10" s="4">
         <v>0</v>
       </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="4">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="F10" s="4">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G10" s="4">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H10" s="4">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I10" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4">
         <v>0</v>
       </c>
       <c r="K10" s="4">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L10" s="4">
-        <v>132</v>
-      </c>
-      <c r="M10" s="4">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4"/>
+        <v>141</v>
+      </c>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4">
+        <v>103</v>
+      </c>
       <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
+      <c r="P10" s="4">
+        <v>103</v>
+      </c>
       <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
+      <c r="R10" s="4">
+        <v>114</v>
+      </c>
       <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
+      <c r="T10" s="4">
+        <v>95</v>
+      </c>
+      <c r="U10" s="4">
+        <v>106</v>
+      </c>
+      <c r="V10" s="4">
+        <v>97</v>
+      </c>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
-      <c r="AB10" s="4"/>
-      <c r="AC10" s="4"/>
+      <c r="Y10" s="4">
+        <v>101</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>112</v>
+      </c>
+      <c r="AA10" s="4">
+        <v>113</v>
+      </c>
+      <c r="AB10" s="4">
+        <v>101</v>
+      </c>
+      <c r="AC10" s="4">
+        <v>111</v>
+      </c>
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
-      <c r="AF10" s="4"/>
+      <c r="AF10" s="4">
+        <v>122</v>
+      </c>
       <c r="AG10" s="9">
-        <v>712</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="4">
-        <v>0</v>
-      </c>
+      <c r="B11" s="4"/>
       <c r="C11" s="4">
         <v>0</v>
       </c>
       <c r="D11" s="4">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E11" s="4">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F11" s="4">
-        <v>129</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
       <c r="I11" s="4">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J11" s="4">
         <v>0</v>
       </c>
       <c r="K11" s="4">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="L11" s="4">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M11" s="4">
-        <v>107</v>
-      </c>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
+        <v>108</v>
+      </c>
+      <c r="N11" s="4">
+        <v>105</v>
+      </c>
+      <c r="O11" s="4">
+        <v>102</v>
+      </c>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
+      <c r="R11" s="4">
+        <v>95</v>
+      </c>
+      <c r="S11" s="4">
+        <v>125</v>
+      </c>
+      <c r="T11" s="4">
+        <v>110</v>
+      </c>
+      <c r="U11" s="4">
+        <v>111</v>
+      </c>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
-      <c r="AB11" s="4"/>
+      <c r="Y11" s="4">
+        <v>103</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>111</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>106</v>
+      </c>
+      <c r="AB11" s="4">
+        <v>108</v>
+      </c>
       <c r="AC11" s="4"/>
-      <c r="AD11" s="4"/>
+      <c r="AD11" s="4">
+        <v>157</v>
+      </c>
       <c r="AE11" s="4"/>
-      <c r="AF11" s="4"/>
+      <c r="AF11" s="4">
+        <v>115</v>
+      </c>
       <c r="AG11" s="9">
-        <v>737</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="4">
-        <v>0</v>
-      </c>
+      <c r="B12" s="4"/>
       <c r="C12" s="4">
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E12" s="4">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F12" s="4">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G12" s="4">
-        <v>135</v>
-      </c>
-      <c r="H12" s="4">
-        <v>0</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="H12" s="4"/>
       <c r="I12" s="4">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="J12" s="4">
         <v>0</v>
       </c>
       <c r="K12" s="4">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="L12" s="4">
+        <v>121</v>
+      </c>
+      <c r="M12" s="4">
         <v>109</v>
-      </c>
-      <c r="M12" s="4">
-        <v>101</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
+      <c r="R12" s="4">
+        <v>107</v>
+      </c>
+      <c r="S12" s="4">
+        <v>118</v>
+      </c>
+      <c r="T12" s="4">
+        <v>107</v>
+      </c>
+      <c r="U12" s="4">
+        <v>112</v>
+      </c>
       <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
+      <c r="W12" s="4">
+        <v>125</v>
+      </c>
       <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
+      <c r="Y12" s="4">
+        <v>110</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>111</v>
+      </c>
       <c r="AA12" s="4"/>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4"/>
+      <c r="AB12" s="4">
+        <v>109</v>
+      </c>
+      <c r="AC12" s="4">
+        <v>107</v>
+      </c>
+      <c r="AD12" s="4">
+        <v>162</v>
+      </c>
       <c r="AE12" s="4"/>
-      <c r="AF12" s="4"/>
+      <c r="AF12" s="4">
+        <v>111</v>
+      </c>
       <c r="AG12" s="9">
-        <v>823</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1807,62 +2009,78 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C13" s="4">
         <v>0</v>
       </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
+      <c r="D13" s="4"/>
       <c r="E13" s="4">
+        <v>103</v>
+      </c>
+      <c r="F13" s="4">
+        <v>7</v>
+      </c>
+      <c r="G13" s="4">
+        <v>92</v>
+      </c>
+      <c r="H13" s="4">
+        <v>78</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
+        <v>66</v>
+      </c>
+      <c r="L13" s="4">
+        <v>108</v>
+      </c>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4">
         <v>101</v>
       </c>
-      <c r="F13" s="4">
-        <v>3</v>
-      </c>
-      <c r="G13" s="4">
-        <v>86</v>
-      </c>
-      <c r="H13" s="4">
-        <v>71</v>
-      </c>
-      <c r="I13" s="4">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4">
-        <v>56</v>
-      </c>
-      <c r="L13" s="4">
-        <v>100</v>
-      </c>
-      <c r="M13" s="4">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
+      <c r="O13" s="4">
+        <v>108</v>
+      </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
+      <c r="R13" s="4">
+        <v>108</v>
+      </c>
+      <c r="S13" s="4">
+        <v>94</v>
+      </c>
       <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
+      <c r="U13" s="4">
+        <v>77</v>
+      </c>
       <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
+      <c r="W13" s="4">
+        <v>67</v>
+      </c>
       <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4"/>
-      <c r="AB13" s="4"/>
-      <c r="AC13" s="4"/>
+      <c r="Y13" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>102</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>103</v>
+      </c>
+      <c r="AB13" s="4">
+        <v>106</v>
+      </c>
+      <c r="AC13" s="4">
+        <v>112</v>
+      </c>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="9">
-        <v>489</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -1870,125 +2088,167 @@
         <v>15</v>
       </c>
       <c r="B14" s="4">
+        <v>106</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <v>108</v>
+      </c>
+      <c r="E14" s="4">
+        <v>107</v>
+      </c>
+      <c r="F14" s="4">
+        <v>110</v>
+      </c>
+      <c r="G14" s="4">
+        <v>148</v>
+      </c>
+      <c r="H14" s="4">
+        <v>124</v>
+      </c>
+      <c r="I14" s="4">
+        <v>81</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4">
+        <v>127</v>
+      </c>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4">
+        <v>3</v>
+      </c>
+      <c r="O14" s="4">
+        <v>56</v>
+      </c>
+      <c r="P14" s="4">
+        <v>94</v>
+      </c>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4">
+        <v>99</v>
+      </c>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4">
         <v>97</v>
       </c>
-      <c r="C14" s="4">
-        <v>0</v>
-      </c>
-      <c r="D14" s="4">
-        <v>99</v>
-      </c>
-      <c r="E14" s="4">
-        <v>102</v>
-      </c>
-      <c r="F14" s="4">
-        <v>101</v>
-      </c>
-      <c r="G14" s="4">
-        <v>133</v>
-      </c>
-      <c r="H14" s="4">
-        <v>108</v>
-      </c>
-      <c r="I14" s="4">
-        <v>63</v>
-      </c>
-      <c r="J14" s="4">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4">
-        <v>114</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
       <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
+      <c r="V14" s="4">
+        <v>103</v>
+      </c>
+      <c r="W14" s="4">
+        <v>90</v>
+      </c>
       <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
-      <c r="AB14" s="4"/>
-      <c r="AC14" s="4"/>
+      <c r="Y14" s="4">
+        <v>106</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>93</v>
+      </c>
+      <c r="AA14" s="4">
+        <v>104</v>
+      </c>
+      <c r="AB14" s="4">
+        <v>111</v>
+      </c>
+      <c r="AC14" s="4">
+        <v>100</v>
+      </c>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
-      <c r="AF14" s="4"/>
+      <c r="AF14" s="4">
+        <v>79</v>
+      </c>
       <c r="AG14" s="9">
-        <v>817</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="4">
-        <v>0</v>
-      </c>
+      <c r="B15" s="4"/>
       <c r="C15" s="4">
         <v>0</v>
       </c>
       <c r="D15" s="4">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E15" s="4">
-        <v>97</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="F15" s="4"/>
       <c r="G15" s="4">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H15" s="4">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="I15" s="4">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="J15" s="4">
         <v>0</v>
       </c>
       <c r="K15" s="4">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="L15" s="4">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="M15" s="4">
-        <v>107</v>
-      </c>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
+        <v>110</v>
+      </c>
+      <c r="N15" s="4">
+        <v>116</v>
+      </c>
+      <c r="O15" s="4">
+        <v>104</v>
+      </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
+      <c r="R15" s="4">
+        <v>96</v>
+      </c>
+      <c r="S15" s="4">
+        <v>100</v>
+      </c>
+      <c r="T15" s="4">
+        <v>101</v>
+      </c>
       <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
+      <c r="V15" s="4">
+        <v>102</v>
+      </c>
+      <c r="W15" s="4">
+        <v>79</v>
+      </c>
       <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="4"/>
-      <c r="AB15" s="4"/>
-      <c r="AC15" s="4"/>
+      <c r="Y15" s="4">
+        <v>110</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>103</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>104</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>109</v>
+      </c>
+      <c r="AC15" s="4">
+        <v>108</v>
+      </c>
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="9">
-        <v>737</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -1996,62 +2256,82 @@
         <v>24</v>
       </c>
       <c r="B16" s="4">
+        <v>117</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
+        <v>114</v>
+      </c>
+      <c r="E16" s="4">
+        <v>114</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4">
+        <v>113</v>
+      </c>
+      <c r="H16" s="4">
+        <v>79</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <v>72</v>
+      </c>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4">
+        <v>122</v>
+      </c>
+      <c r="N16" s="4">
         <v>109</v>
       </c>
-      <c r="C16" s="4">
-        <v>0</v>
-      </c>
-      <c r="D16" s="4">
-        <v>106</v>
-      </c>
-      <c r="E16" s="4">
-        <v>105</v>
-      </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4">
-        <v>103</v>
-      </c>
-      <c r="H16" s="4">
-        <v>67</v>
-      </c>
-      <c r="I16" s="4">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4">
-        <v>0</v>
-      </c>
-      <c r="K16" s="4">
-        <v>66</v>
-      </c>
-      <c r="L16" s="4">
-        <v>0</v>
-      </c>
-      <c r="M16" s="4">
-        <v>109</v>
-      </c>
-      <c r="N16" s="4"/>
       <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
+      <c r="P16" s="4">
+        <v>115</v>
+      </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
+      <c r="S16" s="4">
+        <v>99</v>
+      </c>
+      <c r="T16" s="4">
+        <v>77</v>
+      </c>
+      <c r="U16" s="4">
+        <v>97</v>
+      </c>
+      <c r="V16" s="4">
+        <v>105</v>
+      </c>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="4"/>
-      <c r="AB16" s="4"/>
-      <c r="AC16" s="4"/>
-      <c r="AD16" s="4"/>
+      <c r="Y16" s="4">
+        <v>104</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>119</v>
+      </c>
+      <c r="AA16" s="4">
+        <v>114</v>
+      </c>
+      <c r="AB16" s="4">
+        <v>122</v>
+      </c>
+      <c r="AC16" s="4">
+        <v>122</v>
+      </c>
+      <c r="AD16" s="4">
+        <v>133</v>
+      </c>
       <c r="AE16" s="4"/>
-      <c r="AF16" s="4"/>
+      <c r="AF16" s="4">
+        <v>93</v>
+      </c>
       <c r="AG16" s="9">
-        <v>665</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -2059,188 +2339,240 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C17" s="4">
         <v>0</v>
       </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
+      <c r="D17" s="4"/>
       <c r="E17" s="4">
+        <v>113</v>
+      </c>
+      <c r="F17" s="4">
+        <v>133</v>
+      </c>
+      <c r="G17" s="4">
+        <v>134</v>
+      </c>
+      <c r="H17" s="4">
+        <v>16</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4">
+        <v>103</v>
+      </c>
+      <c r="L17" s="4">
+        <v>118</v>
+      </c>
+      <c r="M17" s="4">
+        <v>113</v>
+      </c>
+      <c r="N17" s="4">
+        <v>107</v>
+      </c>
+      <c r="O17" s="4">
         <v>104</v>
       </c>
-      <c r="F17" s="4">
-        <v>127</v>
-      </c>
-      <c r="G17" s="4">
-        <v>131</v>
-      </c>
-      <c r="H17" s="4">
-        <v>7</v>
-      </c>
-      <c r="I17" s="4">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4">
-        <v>100</v>
-      </c>
-      <c r="L17" s="4">
-        <v>109</v>
-      </c>
-      <c r="M17" s="4">
-        <v>99</v>
-      </c>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
+      <c r="R17" s="4">
+        <v>102</v>
+      </c>
+      <c r="S17" s="4">
+        <v>116</v>
+      </c>
       <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
+      <c r="U17" s="4">
+        <v>94</v>
+      </c>
+      <c r="V17" s="4">
+        <v>100</v>
+      </c>
+      <c r="W17" s="4">
+        <v>103</v>
+      </c>
       <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="4"/>
-      <c r="AB17" s="4"/>
-      <c r="AC17" s="4"/>
+      <c r="Y17" s="4">
+        <v>103</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>104</v>
+      </c>
+      <c r="AA17" s="4">
+        <v>108</v>
+      </c>
+      <c r="AB17" s="4">
+        <v>106</v>
+      </c>
+      <c r="AC17" s="4">
+        <v>104</v>
+      </c>
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
-      <c r="AF17" s="4"/>
+      <c r="AF17" s="4">
+        <v>119</v>
+      </c>
       <c r="AG17" s="9">
-        <v>775</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4">
-        <v>0</v>
-      </c>
+      <c r="B18" s="4"/>
       <c r="C18" s="4">
         <v>0</v>
       </c>
       <c r="D18" s="4">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E18" s="4">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F18" s="4">
-        <v>108</v>
-      </c>
-      <c r="G18" s="4">
-        <v>0</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="G18" s="4"/>
       <c r="H18" s="4">
-        <v>83</v>
-      </c>
-      <c r="I18" s="4">
-        <v>0</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="I18" s="4"/>
       <c r="J18" s="4">
         <v>0</v>
       </c>
       <c r="K18" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L18" s="4">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M18" s="4">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
+      <c r="O18" s="4">
+        <v>110</v>
+      </c>
+      <c r="P18" s="4">
+        <v>107</v>
+      </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
+      <c r="S18" s="4">
+        <v>104</v>
+      </c>
       <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
+      <c r="U18" s="4">
+        <v>82</v>
+      </c>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
-      <c r="AB18" s="4"/>
-      <c r="AC18" s="4"/>
-      <c r="AD18" s="4"/>
+      <c r="AB18" s="4">
+        <v>104</v>
+      </c>
+      <c r="AC18" s="4">
+        <v>106</v>
+      </c>
+      <c r="AD18" s="4">
+        <v>124</v>
+      </c>
       <c r="AE18" s="4"/>
-      <c r="AF18" s="4"/>
+      <c r="AF18" s="4">
+        <v>88</v>
+      </c>
       <c r="AG18" s="9">
-        <v>673</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="4">
-        <v>0</v>
-      </c>
+      <c r="B19" s="4"/>
       <c r="C19" s="4">
         <v>0</v>
       </c>
       <c r="D19" s="4">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="E19" s="4">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="F19" s="4">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G19" s="4">
+        <v>114</v>
+      </c>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4">
+        <v>98</v>
+      </c>
+      <c r="L19" s="4">
+        <v>114</v>
+      </c>
+      <c r="M19" s="4">
+        <v>109</v>
+      </c>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4">
+        <v>105</v>
+      </c>
+      <c r="P19" s="4">
+        <v>106</v>
+      </c>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4">
         <v>107</v>
       </c>
-      <c r="H19" s="4">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4">
-        <v>89</v>
-      </c>
-      <c r="L19" s="4">
+      <c r="S19" s="4"/>
+      <c r="T19" s="4">
+        <v>108</v>
+      </c>
+      <c r="U19" s="4">
+        <v>103</v>
+      </c>
+      <c r="V19" s="4">
+        <v>102</v>
+      </c>
+      <c r="W19" s="4">
+        <v>96</v>
+      </c>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4">
+        <v>108</v>
+      </c>
+      <c r="Z19" s="4">
         <v>104</v>
       </c>
-      <c r="M19" s="4">
-        <v>99</v>
-      </c>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
+      <c r="AA19" s="4">
+        <v>111</v>
+      </c>
       <c r="AB19" s="4"/>
-      <c r="AC19" s="4"/>
-      <c r="AD19" s="4"/>
+      <c r="AC19" s="4">
+        <v>105</v>
+      </c>
+      <c r="AD19" s="4">
+        <v>130</v>
+      </c>
       <c r="AE19" s="4"/>
-      <c r="AF19" s="4"/>
+      <c r="AF19" s="4">
+        <v>102</v>
+      </c>
       <c r="AG19" s="9">
-        <v>696</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2248,62 +2580,94 @@
         <v>21</v>
       </c>
       <c r="B20" s="6">
-        <v>782</v>
+        <v>861</v>
       </c>
       <c r="C20" s="6">
         <v>0</v>
       </c>
       <c r="D20" s="6">
-        <v>1336</v>
+        <v>1448</v>
       </c>
       <c r="E20" s="6">
-        <v>1530</v>
+        <v>1670</v>
       </c>
       <c r="F20" s="6">
-        <v>1466</v>
+        <v>1560</v>
       </c>
       <c r="G20" s="6">
-        <v>1546</v>
+        <v>1695</v>
       </c>
       <c r="H20" s="6">
-        <v>1263</v>
+        <v>1409</v>
       </c>
       <c r="I20" s="6">
-        <v>611</v>
+        <v>701</v>
       </c>
       <c r="J20" s="6">
         <v>0</v>
       </c>
       <c r="K20" s="6">
-        <v>1379</v>
+        <v>1535</v>
       </c>
       <c r="L20" s="6">
-        <v>1473</v>
+        <v>1604</v>
       </c>
       <c r="M20" s="6">
-        <v>1410</v>
-      </c>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
+        <v>1563</v>
+      </c>
+      <c r="N20" s="6">
+        <v>1284</v>
+      </c>
+      <c r="O20" s="6">
+        <v>1362</v>
+      </c>
+      <c r="P20" s="6">
+        <v>976</v>
+      </c>
       <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
-      <c r="U20" s="6"/>
-      <c r="V20" s="6"/>
-      <c r="W20" s="6"/>
+      <c r="R20" s="6">
+        <v>1305</v>
+      </c>
+      <c r="S20" s="6">
+        <v>1527</v>
+      </c>
+      <c r="T20" s="6">
+        <v>1430</v>
+      </c>
+      <c r="U20" s="6">
+        <v>1319</v>
+      </c>
+      <c r="V20" s="6">
+        <v>1367</v>
+      </c>
+      <c r="W20" s="6">
+        <v>867</v>
+      </c>
       <c r="X20" s="6"/>
-      <c r="Y20" s="6"/>
-      <c r="Z20" s="6"/>
-      <c r="AA20" s="6"/>
-      <c r="AB20" s="6"/>
-      <c r="AC20" s="6"/>
-      <c r="AD20" s="6"/>
+      <c r="Y20" s="6">
+        <v>1525</v>
+      </c>
+      <c r="Z20" s="6">
+        <v>1482</v>
+      </c>
+      <c r="AA20" s="6">
+        <v>1317</v>
+      </c>
+      <c r="AB20" s="6">
+        <v>1647</v>
+      </c>
+      <c r="AC20" s="6">
+        <v>1590</v>
+      </c>
+      <c r="AD20" s="6">
+        <v>1254</v>
+      </c>
       <c r="AE20" s="6"/>
-      <c r="AF20" s="6"/>
+      <c r="AF20" s="6">
+        <v>1515</v>
+      </c>
       <c r="AG20" s="10">
-        <v>12796</v>
+        <v>35813</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
@@ -2370,7 +2734,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>2.4513888888888888</v>
+        <v>3.0079365079365079</v>
       </c>
     </row>
   </sheetData>

--- a/Agustus-2026.xlsx
+++ b/Agustus-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Agent_Retention\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{269E6FB9-E4F7-4920-9381-60E53D88FCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B89D29-4849-41D1-A0D3-117BC1FD954F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -578,10 +578,10 @@
         <v>1357</v>
       </c>
       <c r="D2" s="9">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E2" s="13">
-        <v>3.6666666666666665</v>
+        <v>4.2380952380952381</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -597,10 +597,10 @@
         <v>1418</v>
       </c>
       <c r="D3" s="9">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E3" s="13">
-        <v>2.5714285714285716</v>
+        <v>2.8571428571428572</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -616,10 +616,10 @@
         <v>1626</v>
       </c>
       <c r="D4" s="9">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="E4" s="13">
-        <v>3</v>
+        <v>3.8571428571428572</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -635,10 +635,10 @@
         <v>1414</v>
       </c>
       <c r="D5" s="9">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E5" s="13">
-        <v>3.5238095238095237</v>
+        <v>3.8095238095238093</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -654,10 +654,10 @@
         <v>1262</v>
       </c>
       <c r="D6" s="9">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E6" s="13">
-        <v>4.0952380952380949</v>
+        <v>4.5714285714285712</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -673,10 +673,10 @@
         <v>412</v>
       </c>
       <c r="D7" s="9">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E7" s="13">
-        <v>1.3333333333333333</v>
+        <v>1.4761904761904763</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -692,10 +692,10 @@
         <v>1606</v>
       </c>
       <c r="D8" s="9">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E8" s="13">
-        <v>3.0952380952380953</v>
+        <v>3.5714285714285716</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -711,10 +711,10 @@
         <v>1659</v>
       </c>
       <c r="D9" s="9">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="E9" s="13">
-        <v>3.6666666666666665</v>
+        <v>4.4285714285714288</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -730,10 +730,10 @@
         <v>1412</v>
       </c>
       <c r="D10" s="9">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E10" s="13">
-        <v>3.4285714285714284</v>
+        <v>3.8095238095238093</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -749,10 +749,10 @@
         <v>1636</v>
       </c>
       <c r="D11" s="9">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E11" s="13">
-        <v>4</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -768,10 +768,10 @@
         <v>1425</v>
       </c>
       <c r="D12" s="9">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E12" s="13">
-        <v>3.8095238095238093</v>
+        <v>4.0476190476190474</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="1"/>
@@ -787,10 +787,10 @@
         <v>1117</v>
       </c>
       <c r="D13" s="9">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="E13" s="13">
-        <v>3.1428571428571428</v>
+        <v>4.0476190476190474</v>
       </c>
       <c r="F13" s="1"/>
       <c r="H13" s="1"/>
@@ -806,10 +806,10 @@
         <v>1352</v>
       </c>
       <c r="D14" s="9">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E14" s="13">
-        <v>2.1904761904761907</v>
+        <v>2.9047619047619047</v>
       </c>
       <c r="F14" s="1"/>
       <c r="H14" s="1"/>
@@ -825,10 +825,10 @@
         <v>1559</v>
       </c>
       <c r="D15" s="9">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E15" s="13">
-        <v>2.1904761904761907</v>
+        <v>2.5238095238095237</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -844,10 +844,10 @@
         <v>1453</v>
       </c>
       <c r="D16" s="9">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E16" s="13">
-        <v>3.1904761904761907</v>
+        <v>3.8571428571428572</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -863,10 +863,10 @@
         <v>1648</v>
       </c>
       <c r="D17" s="9">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E17" s="13">
-        <v>2.9047619047619047</v>
+        <v>3.6190476190476191</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -882,10 +882,10 @@
         <v>1268</v>
       </c>
       <c r="D18" s="9">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E18" s="13">
-        <v>1.1904761904761905</v>
+        <v>1.5238095238095237</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -901,11 +901,12 @@
         <v>1650</v>
       </c>
       <c r="D19" s="9">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E19" s="13">
-        <v>3.1428571428571428</v>
-      </c>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -918,11 +919,12 @@
         <v>25274</v>
       </c>
       <c r="D20" s="10">
-        <v>1137</v>
+        <v>1319</v>
       </c>
       <c r="E20" s="14">
-        <v>3.0079365079365079</v>
-      </c>
+        <v>3.4894179894179893</v>
+      </c>
+      <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F21" s="1"/>
@@ -2734,7 +2736,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>3.0079365079365079</v>
+        <v>3.4894179894179893</v>
       </c>
     </row>
   </sheetData>
